--- a/5. Secondary_Team_Map.xlsx
+++ b/5. Secondary_Team_Map.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Downloads\Python Environment\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B432C5E3-6209-4147-850F-B35D5D5BCF3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17580"/>
+    <workbookView xWindow="14460" yWindow="1260" windowWidth="25335" windowHeight="19875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="31">
   <si>
     <t>Player Name</t>
   </si>
@@ -108,12 +109,21 @@
   </si>
   <si>
     <t>Josh Parker</t>
+  </si>
+  <si>
+    <t>Cara Murray</t>
+  </si>
+  <si>
+    <t>Waringstown</t>
+  </si>
+  <si>
+    <t>Lucia Derby</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -151,10 +161,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -434,8 +443,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" bestFit="1" customWidth="1"/>
@@ -475,7 +484,7 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5" t="s">
@@ -507,7 +516,7 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" t="s">
         <v>7</v>
       </c>
       <c r="B9" t="s">
@@ -515,7 +524,7 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="A10" t="s">
         <v>8</v>
       </c>
       <c r="B10" t="s">
@@ -531,7 +540,7 @@
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="A12" t="s">
         <v>4</v>
       </c>
       <c r="B12" t="s">
@@ -539,7 +548,7 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="A13" t="s">
         <v>9</v>
       </c>
       <c r="B13" t="s">
@@ -547,7 +556,7 @@
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="A14" t="s">
         <v>5</v>
       </c>
       <c r="B14" t="s">
@@ -595,7 +604,7 @@
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="A20" t="s">
         <v>10</v>
       </c>
       <c r="B20" t="s">
@@ -611,7 +620,7 @@
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="A22" t="s">
         <v>11</v>
       </c>
       <c r="B22" t="s">
@@ -619,7 +628,7 @@
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+      <c r="A23" t="s">
         <v>12</v>
       </c>
       <c r="B23" t="s">
@@ -627,7 +636,7 @@
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="A24" t="s">
         <v>13</v>
       </c>
       <c r="B24" t="s">
@@ -650,8 +659,24 @@
         <v>3</v>
       </c>
     </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState ref="A2:B26">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B26">
     <sortCondition ref="A2"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/5. Secondary_Team_Map.xlsx
+++ b/5. Secondary_Team_Map.xlsx
@@ -5,27 +5,38 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Downloads\Python Environment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B432C5E3-6209-4147-850F-B35D5D5BCF3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{158DBECB-B879-4BE8-9638-859EFD300E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14460" yWindow="1260" windowWidth="25335" windowHeight="19875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15900" yWindow="1110" windowWidth="25335" windowHeight="19875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="41">
   <si>
     <t>Player Name</t>
   </si>
@@ -33,9 +44,6 @@
     <t>Team</t>
   </si>
   <si>
-    <t>Dylan McCann</t>
-  </si>
-  <si>
     <t>NCU Pathway XI</t>
   </si>
   <si>
@@ -118,6 +126,39 @@
   </si>
   <si>
     <t>Lucia Derby</t>
+  </si>
+  <si>
+    <t>Ellie Bullick </t>
+  </si>
+  <si>
+    <t>North Down</t>
+  </si>
+  <si>
+    <t>Sophie Hughes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olivia Watt </t>
+  </si>
+  <si>
+    <t>Cregagh</t>
+  </si>
+  <si>
+    <t>Laurelvale</t>
+  </si>
+  <si>
+    <t>Adam Walker</t>
+  </si>
+  <si>
+    <t>PSNI</t>
+  </si>
+  <si>
+    <t>Charlie Shannon</t>
+  </si>
+  <si>
+    <t>Dylan McCann (Lisburn)</t>
+  </si>
+  <si>
+    <t>Naomi Matthews</t>
   </si>
 </sst>
 </file>
@@ -444,11 +485,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -461,218 +502,266 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B20" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B26" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" t="s">
         <v>28</v>
-      </c>
-      <c r="B27" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>30</v>
       </c>
-      <c r="B28" t="s">
-        <v>29</v>
+      <c r="B29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/5. Secondary_Team_Map.xlsx
+++ b/5. Secondary_Team_Map.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +36,11 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -65,10 +70,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -420,12 +426,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Player Name</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
